--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F810C3-072A-4222-A82A-B72D61918AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D1C831-C35B-4573-9FE5-2078E77628BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1044" yWindow="2964" windowWidth="17280" windowHeight="8964" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Staff" sheetId="1" r:id="rId1"/>
+    <sheet name="Staff 2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>Nome</t>
   </si>
@@ -49,6 +50,27 @@
   </si>
   <si>
     <t>Cedrino</t>
+  </si>
+  <si>
+    <t>Caniato</t>
+  </si>
+  <si>
+    <t>Nicola</t>
+  </si>
+  <si>
+    <t>Raffaele</t>
+  </si>
+  <si>
+    <t>Garofalo</t>
+  </si>
+  <si>
+    <t>Buzzoni</t>
+  </si>
+  <si>
+    <t>Matteo</t>
+  </si>
+  <si>
+    <t>Chinaglia</t>
   </si>
 </sst>
 </file>
@@ -425,4 +447,69 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D01CC48A-C7CA-48AF-BC9F-58D9577498A5}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D1C831-C35B-4573-9FE5-2078E77628BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7DBD3E-A51D-471C-A5AE-672AC58CF427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1044" yWindow="2964" windowWidth="17280" windowHeight="8964" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Staff" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>Nome</t>
   </si>
@@ -71,6 +71,12 @@
   </si>
   <si>
     <t>Chinaglia</t>
+  </si>
+  <si>
+    <t>Davide</t>
+  </si>
+  <si>
+    <t>Della Volpe</t>
   </si>
 </sst>
 </file>
@@ -397,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -442,6 +448,17 @@
       </c>
       <c r="C4">
         <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -455,13 +472,13 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -511,5 +528,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7DBD3E-A51D-471C-A5AE-672AC58CF427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6925B119-6A09-4A7A-BCDE-5046BB70AF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Staff" sheetId="1" r:id="rId1"/>
-    <sheet name="Staff 2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Nome</t>
   </si>
@@ -35,48 +34,6 @@
   </si>
   <si>
     <t>Numero</t>
-  </si>
-  <si>
-    <t>Daniel</t>
-  </si>
-  <si>
-    <t>Marchi</t>
-  </si>
-  <si>
-    <t>Cava</t>
-  </si>
-  <si>
-    <t>Luca</t>
-  </si>
-  <si>
-    <t>Cedrino</t>
-  </si>
-  <si>
-    <t>Caniato</t>
-  </si>
-  <si>
-    <t>Nicola</t>
-  </si>
-  <si>
-    <t>Raffaele</t>
-  </si>
-  <si>
-    <t>Garofalo</t>
-  </si>
-  <si>
-    <t>Buzzoni</t>
-  </si>
-  <si>
-    <t>Matteo</t>
-  </si>
-  <si>
-    <t>Chinaglia</t>
-  </si>
-  <si>
-    <t>Davide</t>
-  </si>
-  <si>
-    <t>Della Volpe</t>
   </si>
 </sst>
 </file>
@@ -403,7 +360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -417,117 +374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D01CC48A-C7CA-48AF-BC9F-58D9577498A5}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
 </file>
--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6925B119-6A09-4A7A-BCDE-5046BB70AF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3117945E-C8E8-4C27-AB53-4D4E6CF605F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="300" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Staff" sheetId="1" r:id="rId1"/>
+    <sheet name="Esempio" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>

--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3117945E-C8E8-4C27-AB53-4D4E6CF605F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8600F91E-D622-4EE0-B8E7-DC51E18BFC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="300" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Esempio" sheetId="1" r:id="rId1"/>
+    <sheet name="Piadineria La Salsiccia" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Nome</t>
   </si>
@@ -34,6 +34,66 @@
   </si>
   <si>
     <t>Numero</t>
+  </si>
+  <si>
+    <t>Kevin</t>
+  </si>
+  <si>
+    <t>Castellan</t>
+  </si>
+  <si>
+    <t>Soufiane</t>
+  </si>
+  <si>
+    <t>Khechab</t>
+  </si>
+  <si>
+    <t>Gabriele</t>
+  </si>
+  <si>
+    <t>Barbierato</t>
+  </si>
+  <si>
+    <t>Davide</t>
+  </si>
+  <si>
+    <t>Della Volpe</t>
+  </si>
+  <si>
+    <t>Luca</t>
+  </si>
+  <si>
+    <t>Cedrino</t>
+  </si>
+  <si>
+    <t>Sabil</t>
+  </si>
+  <si>
+    <t>Allal</t>
+  </si>
+  <si>
+    <t>Oussama</t>
+  </si>
+  <si>
+    <t>Mostatira</t>
+  </si>
+  <si>
+    <t>Mattia Ayrton</t>
+  </si>
+  <si>
+    <t>Mariotto</t>
+  </si>
+  <si>
+    <t>Raffaele</t>
+  </si>
+  <si>
+    <t>Garofalo</t>
+  </si>
+  <si>
+    <t>Alex</t>
+  </si>
+  <si>
+    <t>Bergo</t>
   </si>
 </sst>
 </file>
@@ -360,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -374,6 +434,116 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8600F91E-D622-4EE0-B8E7-DC51E18BFC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1E7CF6-0416-4701-802D-A6D577F887F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -491,10 +491,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
         <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
       </c>
       <c r="C7">
         <v>6</v>

--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1E7CF6-0416-4701-802D-A6D577F887F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B28218-B922-415B-B03C-F7914481C914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Piadineria La Salsiccia" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Nome</t>
   </si>
@@ -94,6 +95,12 @@
   </si>
   <si>
     <t>Bergo</t>
+  </si>
+  <si>
+    <t>Capitano</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
 </sst>
 </file>
@@ -420,10 +427,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -433,8 +440,11 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -445,7 +455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -456,7 +466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -467,7 +477,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -477,8 +487,11 @@
       <c r="C5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -489,7 +502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -500,7 +513,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -511,7 +524,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -522,7 +535,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -533,7 +546,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>21</v>
       </c>

--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B28218-B922-415B-B03C-F7914481C914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D8F233-F089-41B8-B5A1-0C6DCB0AEB23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Piadineria La Salsiccia" sheetId="1" r:id="rId1"/>
+    <sheet name="AS Bancatore" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
   <si>
     <t>Nome</t>
   </si>
@@ -73,12 +73,6 @@
     <t>Allal</t>
   </si>
   <si>
-    <t>Oussama</t>
-  </si>
-  <si>
-    <t>Mostatira</t>
-  </si>
-  <si>
     <t>Mattia Ayrton</t>
   </si>
   <si>
@@ -101,6 +95,72 @@
   </si>
   <si>
     <t>C</t>
+  </si>
+  <si>
+    <t>Riccardo</t>
+  </si>
+  <si>
+    <t>Broglio</t>
+  </si>
+  <si>
+    <t>Nicolò</t>
+  </si>
+  <si>
+    <t>Marangoni</t>
+  </si>
+  <si>
+    <t>Matteo</t>
+  </si>
+  <si>
+    <t>Longo</t>
+  </si>
+  <si>
+    <t>Mattia</t>
+  </si>
+  <si>
+    <t>Zago</t>
+  </si>
+  <si>
+    <t>Savioli</t>
+  </si>
+  <si>
+    <t>Ignazio</t>
+  </si>
+  <si>
+    <t>Badalì</t>
+  </si>
+  <si>
+    <t>Gianluca</t>
+  </si>
+  <si>
+    <t>Frezzati</t>
+  </si>
+  <si>
+    <t>Federico</t>
+  </si>
+  <si>
+    <t>Mascellani</t>
+  </si>
+  <si>
+    <t>Alberto</t>
+  </si>
+  <si>
+    <t>Osti</t>
+  </si>
+  <si>
+    <t>Rossi</t>
+  </si>
+  <si>
+    <t>Nicola</t>
+  </si>
+  <si>
+    <t>Baroni</t>
+  </si>
+  <si>
+    <t>Manuel</t>
+  </si>
+  <si>
+    <t>Medea</t>
   </si>
 </sst>
 </file>
@@ -441,7 +501,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -488,7 +548,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -521,26 +581,26 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10">
         <v>10</v>
@@ -548,13 +608,161 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11">
         <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662A4DF0-DEDD-402B-8014-45CA08C06EFA}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D8F233-F089-41B8-B5A1-0C6DCB0AEB23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A185D6-0ED7-49EE-A424-ED6FDD4157E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Piadineria La Salsiccia" sheetId="1" r:id="rId1"/>
     <sheet name="AS Bancatore" sheetId="3" r:id="rId2"/>
+    <sheet name="All Blacks" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
   <si>
     <t>Nome</t>
   </si>
@@ -161,6 +162,54 @@
   </si>
   <si>
     <t>Medea</t>
+  </si>
+  <si>
+    <t>Giacomo</t>
+  </si>
+  <si>
+    <t>De Simone</t>
+  </si>
+  <si>
+    <t>Martino</t>
+  </si>
+  <si>
+    <t>Granfo</t>
+  </si>
+  <si>
+    <t>Stefano</t>
+  </si>
+  <si>
+    <t>Braghin</t>
+  </si>
+  <si>
+    <t>M.T.P.</t>
+  </si>
+  <si>
+    <t>Bedeschi</t>
+  </si>
+  <si>
+    <t>Nicholas</t>
+  </si>
+  <si>
+    <t>Moschini</t>
+  </si>
+  <si>
+    <t>Girardello</t>
+  </si>
+  <si>
+    <t>Bergantin</t>
+  </si>
+  <si>
+    <t>Filippo</t>
+  </si>
+  <si>
+    <t>Clemente</t>
+  </si>
+  <si>
+    <t>Lorenzetti</t>
+  </si>
+  <si>
+    <t>Biolcati</t>
   </si>
 </sst>
 </file>
@@ -768,4 +817,149 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A5EFFF2-4144-4797-9296-B8D782FF7077}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A185D6-0ED7-49EE-A424-ED6FDD4157E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A01256D-C4A1-46BF-B5DE-37B57CF05FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Piadineria La Salsiccia" sheetId="1" r:id="rId1"/>
     <sheet name="AS Bancatore" sheetId="3" r:id="rId2"/>
     <sheet name="All Blacks" sheetId="4" r:id="rId3"/>
+    <sheet name="Cani" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="78">
   <si>
     <t>Nome</t>
   </si>
@@ -182,9 +183,6 @@
     <t>Braghin</t>
   </si>
   <si>
-    <t>M.T.P.</t>
-  </si>
-  <si>
     <t>Bedeschi</t>
   </si>
   <si>
@@ -210,6 +208,60 @@
   </si>
   <si>
     <t>Biolcati</t>
+  </si>
+  <si>
+    <t>Bresciani</t>
+  </si>
+  <si>
+    <t>Impelliccieri</t>
+  </si>
+  <si>
+    <t>Mourad</t>
+  </si>
+  <si>
+    <t>Echchari</t>
+  </si>
+  <si>
+    <t>Otman</t>
+  </si>
+  <si>
+    <t>Souati</t>
+  </si>
+  <si>
+    <t>Karl</t>
+  </si>
+  <si>
+    <t>Kabasela</t>
+  </si>
+  <si>
+    <t>Alessio</t>
+  </si>
+  <si>
+    <t>Ghirardello</t>
+  </si>
+  <si>
+    <t>Ismail</t>
+  </si>
+  <si>
+    <t>Lorenzo</t>
+  </si>
+  <si>
+    <t>Rezzaghi</t>
+  </si>
+  <si>
+    <t>Tommaso</t>
+  </si>
+  <si>
+    <t>Calzavarini</t>
+  </si>
+  <si>
+    <t>Leonardo</t>
+  </si>
+  <si>
+    <t>Bulgari</t>
+  </si>
+  <si>
+    <t>Tognolo</t>
   </si>
 </sst>
 </file>
@@ -873,7 +925,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
+        <v>60</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -884,7 +939,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -892,10 +947,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
         <v>53</v>
-      </c>
-      <c r="B7" t="s">
-        <v>54</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -906,7 +961,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8">
         <v>8</v>
@@ -917,7 +972,7 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9">
         <v>9</v>
@@ -925,10 +980,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
         <v>57</v>
-      </c>
-      <c r="B10" t="s">
-        <v>58</v>
       </c>
       <c r="C10">
         <v>10</v>
@@ -939,7 +994,7 @@
         <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C11">
         <v>11</v>
@@ -953,10 +1008,147 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12">
         <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90ABF098-E458-4951-9964-B26D79E3C3B0}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A01256D-C4A1-46BF-B5DE-37B57CF05FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684DC0C3-BAA9-4CB3-B732-2A15C993B194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Piadineria La Salsiccia" sheetId="1" r:id="rId1"/>
     <sheet name="AS Bancatore" sheetId="3" r:id="rId2"/>
     <sheet name="All Blacks" sheetId="4" r:id="rId3"/>
     <sheet name="Cani" sheetId="5" r:id="rId4"/>
+    <sheet name="Astolfi Impianti Elettrici" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="91">
   <si>
     <t>Nome</t>
   </si>
@@ -262,6 +263,45 @@
   </si>
   <si>
     <t>Tognolo</t>
+  </si>
+  <si>
+    <t>Nicolas</t>
+  </si>
+  <si>
+    <t>Andriotto</t>
+  </si>
+  <si>
+    <t>Pavan</t>
+  </si>
+  <si>
+    <t>Cavallieri</t>
+  </si>
+  <si>
+    <t>Marco</t>
+  </si>
+  <si>
+    <t>Previato</t>
+  </si>
+  <si>
+    <t>Simeone</t>
+  </si>
+  <si>
+    <t>Elia</t>
+  </si>
+  <si>
+    <t>Naglieri</t>
+  </si>
+  <si>
+    <t>Zanini</t>
+  </si>
+  <si>
+    <t>Munerato</t>
+  </si>
+  <si>
+    <t>Alban</t>
+  </si>
+  <si>
+    <t>Ahmati</t>
   </si>
 </sst>
 </file>
@@ -1154,4 +1194,130 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AD2755E-91E8-4DD1-8529-A65606BD9D72}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684DC0C3-BAA9-4CB3-B732-2A15C993B194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A67DA0E-9927-4971-B356-BC8CEA2CCB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Piadineria La Salsiccia" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="All Blacks" sheetId="4" r:id="rId3"/>
     <sheet name="Cani" sheetId="5" r:id="rId4"/>
     <sheet name="Astolfi Impianti Elettrici" sheetId="6" r:id="rId5"/>
+    <sheet name="Coca Juniors" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="101">
   <si>
     <t>Nome</t>
   </si>
@@ -302,6 +303,36 @@
   </si>
   <si>
     <t>Ahmati</t>
+  </si>
+  <si>
+    <t>Cavallaro</t>
+  </si>
+  <si>
+    <t>Andrea</t>
+  </si>
+  <si>
+    <t>Dobrozi</t>
+  </si>
+  <si>
+    <t>Gian Marco</t>
+  </si>
+  <si>
+    <t>Greggio</t>
+  </si>
+  <si>
+    <t>Dolce</t>
+  </si>
+  <si>
+    <t>Cristian</t>
+  </si>
+  <si>
+    <t>Capuzzo</t>
+  </si>
+  <si>
+    <t>Emanuele</t>
+  </si>
+  <si>
+    <t>Veronese</t>
   </si>
 </sst>
 </file>
@@ -1320,4 +1351,141 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{800F9206-5CAD-4C16-B578-1ABB48D99134}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A67DA0E-9927-4971-B356-BC8CEA2CCB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35747B1A-6039-4DBB-8D77-7E10DDB5738C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Piadineria La Salsiccia" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Cani" sheetId="5" r:id="rId4"/>
     <sheet name="Astolfi Impianti Elettrici" sheetId="6" r:id="rId5"/>
     <sheet name="Coca Juniors" sheetId="7" r:id="rId6"/>
+    <sheet name="Vecchie Glorie Rovigo Calcio" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="114">
   <si>
     <t>Nome</t>
   </si>
@@ -164,9 +165,6 @@
     <t>Manuel</t>
   </si>
   <si>
-    <t>Medea</t>
-  </si>
-  <si>
     <t>Giacomo</t>
   </si>
   <si>
@@ -333,6 +331,48 @@
   </si>
   <si>
     <t>Veronese</t>
+  </si>
+  <si>
+    <t>Zaghi</t>
+  </si>
+  <si>
+    <t>Jacopo</t>
+  </si>
+  <si>
+    <t>Voltolina</t>
+  </si>
+  <si>
+    <t>Zamberlan</t>
+  </si>
+  <si>
+    <t>Dall'Ara</t>
+  </si>
+  <si>
+    <t>Fusco</t>
+  </si>
+  <si>
+    <t>Denis</t>
+  </si>
+  <si>
+    <t>Timpanaro</t>
+  </si>
+  <si>
+    <t>Tosetti</t>
+  </si>
+  <si>
+    <t>Ambrosini</t>
+  </si>
+  <si>
+    <t>Bonin</t>
+  </si>
+  <si>
+    <t>Domenico</t>
+  </si>
+  <si>
+    <t>Iacovino</t>
+  </si>
+  <si>
+    <t>Protti</t>
   </si>
 </sst>
 </file>
@@ -659,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -758,34 +798,23 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11">
         <v>11</v>
       </c>
     </row>
@@ -963,10 +992,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" t="s">
         <v>45</v>
-      </c>
-      <c r="B2" t="s">
-        <v>46</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -974,10 +1003,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
         <v>47</v>
-      </c>
-      <c r="B3" t="s">
-        <v>48</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -985,10 +1014,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" t="s">
         <v>49</v>
-      </c>
-      <c r="B4" t="s">
-        <v>50</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -999,7 +1028,7 @@
         <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -1010,7 +1039,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -1018,10 +1047,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s">
         <v>52</v>
-      </c>
-      <c r="B7" t="s">
-        <v>53</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -1032,7 +1061,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8">
         <v>8</v>
@@ -1043,7 +1072,7 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9">
         <v>9</v>
@@ -1051,10 +1080,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
         <v>56</v>
-      </c>
-      <c r="B10" t="s">
-        <v>57</v>
       </c>
       <c r="C10">
         <v>10</v>
@@ -1065,7 +1094,7 @@
         <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11">
         <v>11</v>
@@ -1079,7 +1108,7 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12">
         <v>18</v>
@@ -1114,7 +1143,7 @@
         <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1122,10 +1151,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" t="s">
         <v>62</v>
-      </c>
-      <c r="B3" t="s">
-        <v>63</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -1133,10 +1162,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" t="s">
         <v>64</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
       </c>
       <c r="C4">
         <v>7</v>
@@ -1144,10 +1173,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" t="s">
         <v>66</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
       </c>
       <c r="C5">
         <v>8</v>
@@ -1155,10 +1184,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" t="s">
         <v>68</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -1169,10 +1198,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7">
         <v>11</v>
@@ -1180,10 +1209,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" t="s">
         <v>71</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
       </c>
       <c r="C8">
         <v>19</v>
@@ -1191,10 +1220,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" t="s">
         <v>73</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
       </c>
       <c r="C9">
         <v>22</v>
@@ -1202,10 +1231,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" t="s">
         <v>75</v>
-      </c>
-      <c r="B10" t="s">
-        <v>76</v>
       </c>
       <c r="C10">
         <v>45</v>
@@ -1216,7 +1245,7 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C11">
         <v>67</v>
@@ -1248,10 +1277,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" t="s">
         <v>78</v>
-      </c>
-      <c r="B2" t="s">
-        <v>79</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1262,7 +1291,7 @@
         <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1273,7 +1302,7 @@
         <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -1281,10 +1310,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" t="s">
         <v>89</v>
-      </c>
-      <c r="B5" t="s">
-        <v>90</v>
       </c>
       <c r="C5">
         <v>7</v>
@@ -1292,10 +1321,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" t="s">
         <v>82</v>
-      </c>
-      <c r="B6" t="s">
-        <v>83</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -1306,7 +1335,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7">
         <v>9</v>
@@ -1314,10 +1343,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
         <v>85</v>
-      </c>
-      <c r="B8" t="s">
-        <v>86</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -1325,10 +1354,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C9">
         <v>11</v>
@@ -1342,7 +1371,7 @@
         <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C10">
         <v>14</v>
@@ -1377,7 +1406,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1388,7 +1417,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -1396,10 +1425,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1407,10 +1436,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -1418,7 +1447,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -1429,10 +1458,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7">
         <v>9</v>
@@ -1440,10 +1469,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -1454,10 +1483,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" t="s">
         <v>97</v>
-      </c>
-      <c r="B9" t="s">
-        <v>98</v>
       </c>
       <c r="C9">
         <v>11</v>
@@ -1465,10 +1494,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" t="s">
         <v>99</v>
-      </c>
-      <c r="B10" t="s">
-        <v>100</v>
       </c>
       <c r="C10">
         <v>23</v>
@@ -1479,10 +1508,125 @@
         <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C11">
         <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B2E3AFC-5F93-4599-9EB1-A950AE3C5AB8}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35747B1A-6039-4DBB-8D77-7E10DDB5738C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F4F7C9-B7C6-445C-B084-B3BCBC318B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Piadineria La Salsiccia" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="Astolfi Impianti Elettrici" sheetId="6" r:id="rId5"/>
     <sheet name="Coca Juniors" sheetId="7" r:id="rId6"/>
     <sheet name="Vecchie Glorie Rovigo Calcio" sheetId="8" r:id="rId7"/>
+    <sheet name="Totani" sheetId="9" r:id="rId8"/>
+    <sheet name="Pink 5ive" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="133">
   <si>
     <t>Nome</t>
   </si>
@@ -373,6 +375,63 @@
   </si>
   <si>
     <t>Protti</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Davì</t>
+  </si>
+  <si>
+    <t>Santarato</t>
+  </si>
+  <si>
+    <t>Stievano</t>
+  </si>
+  <si>
+    <t>Cherubin</t>
+  </si>
+  <si>
+    <t>Crepaldi</t>
+  </si>
+  <si>
+    <t>Paparella</t>
+  </si>
+  <si>
+    <t>Polato</t>
+  </si>
+  <si>
+    <t>Daniele</t>
+  </si>
+  <si>
+    <t>Secco</t>
+  </si>
+  <si>
+    <t>Boscolo</t>
+  </si>
+  <si>
+    <t>Ferraresi</t>
+  </si>
+  <si>
+    <t>Aaron</t>
+  </si>
+  <si>
+    <t>Provito</t>
+  </si>
+  <si>
+    <t>Campion</t>
+  </si>
+  <si>
+    <t>Bedendo</t>
+  </si>
+  <si>
+    <t>Bernardinello</t>
+  </si>
+  <si>
+    <t>Coltro</t>
   </si>
 </sst>
 </file>
@@ -1632,4 +1691,256 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAF217C-E0B4-4151-B7E8-CE5C86D61FBC}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE4569C5-F714-4D8F-9D9F-AD29189E5BA2}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9">
+        <v>63</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F4F7C9-B7C6-445C-B084-B3BCBC318B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62108A63-3568-4752-B1CB-2F45462E4731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Piadineria La Salsiccia" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,9 @@
     <sheet name="Vecchie Glorie Rovigo Calcio" sheetId="8" r:id="rId7"/>
     <sheet name="Totani" sheetId="9" r:id="rId8"/>
     <sheet name="Pink 5ive" sheetId="10" r:id="rId9"/>
+    <sheet name="Fatine FC" sheetId="11" r:id="rId10"/>
+    <sheet name="Barrio Boys" sheetId="13" r:id="rId11"/>
+    <sheet name="Senza Nome" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="168">
   <si>
     <t>Nome</t>
   </si>
@@ -432,6 +435,111 @@
   </si>
   <si>
     <t>Coltro</t>
+  </si>
+  <si>
+    <t>Pietro</t>
+  </si>
+  <si>
+    <t>Segato</t>
+  </si>
+  <si>
+    <t>Giovanni</t>
+  </si>
+  <si>
+    <t>Ballo</t>
+  </si>
+  <si>
+    <t>Marzolla</t>
+  </si>
+  <si>
+    <t>Milan</t>
+  </si>
+  <si>
+    <t>Marini</t>
+  </si>
+  <si>
+    <t>Ghirardi</t>
+  </si>
+  <si>
+    <t>Rossetto</t>
+  </si>
+  <si>
+    <t>Medea</t>
+  </si>
+  <si>
+    <t>Zanforlin</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Strenghetto</t>
+  </si>
+  <si>
+    <t>Bacco</t>
+  </si>
+  <si>
+    <t>Scaranello</t>
+  </si>
+  <si>
+    <t>Noventa</t>
+  </si>
+  <si>
+    <t>Borgato</t>
+  </si>
+  <si>
+    <t>Casarotti</t>
+  </si>
+  <si>
+    <t>Natali</t>
+  </si>
+  <si>
+    <t>Francesco</t>
+  </si>
+  <si>
+    <t>Daddato</t>
+  </si>
+  <si>
+    <t>Lanzoni</t>
+  </si>
+  <si>
+    <t>Politi</t>
+  </si>
+  <si>
+    <t>Seno</t>
+  </si>
+  <si>
+    <t>Niccolò</t>
+  </si>
+  <si>
+    <t>Limaj</t>
+  </si>
+  <si>
+    <t>Nonnato</t>
+  </si>
+  <si>
+    <t>Berardi</t>
+  </si>
+  <si>
+    <t>Marangon</t>
+  </si>
+  <si>
+    <t>Gimmy</t>
+  </si>
+  <si>
+    <t>Manari</t>
+  </si>
+  <si>
+    <t>Micucci</t>
+  </si>
+  <si>
+    <t>Edoardo</t>
+  </si>
+  <si>
+    <t>Cavallari</t>
+  </si>
+  <si>
+    <t>Anzoletti</t>
   </si>
 </sst>
 </file>
@@ -882,6 +990,392 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40728223-3A6A-4F69-B5D3-677705D79A5B}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C11">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F468D78-F21B-4C38-BEE1-9674FBD41E4C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C10">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{293552FE-154F-41A7-B02B-483E9B842FD1}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>156</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662A4DF0-DEDD-402B-8014-45CA08C06EFA}">
   <dimension ref="A1:D12"/>

--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62108A63-3568-4752-B1CB-2F45462E4731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAACABD3-4A89-4380-BD5F-E498C976DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Piadineria La Salsiccia" sheetId="1" r:id="rId1"/>
@@ -22,9 +22,10 @@
     <sheet name="Vecchie Glorie Rovigo Calcio" sheetId="8" r:id="rId7"/>
     <sheet name="Totani" sheetId="9" r:id="rId8"/>
     <sheet name="Pink 5ive" sheetId="10" r:id="rId9"/>
-    <sheet name="Fatine FC" sheetId="11" r:id="rId10"/>
-    <sheet name="Barrio Boys" sheetId="13" r:id="rId11"/>
-    <sheet name="Senza Nome" sheetId="12" r:id="rId12"/>
+    <sheet name="Leoni di Ricky" sheetId="14" r:id="rId10"/>
+    <sheet name="Fatine FC" sheetId="11" r:id="rId11"/>
+    <sheet name="Barrio Boys" sheetId="13" r:id="rId12"/>
+    <sheet name="Senza Nome" sheetId="12" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="176">
   <si>
     <t>Nome</t>
   </si>
@@ -540,6 +541,30 @@
   </si>
   <si>
     <t>Anzoletti</t>
+  </si>
+  <si>
+    <t>Degan</t>
+  </si>
+  <si>
+    <t>Maggio</t>
+  </si>
+  <si>
+    <t>Violato</t>
+  </si>
+  <si>
+    <t>Amin</t>
+  </si>
+  <si>
+    <t>Massaghri</t>
+  </si>
+  <si>
+    <t>Thompson</t>
+  </si>
+  <si>
+    <t>Bortoliero</t>
+  </si>
+  <si>
+    <t>Barzaghideanu</t>
   </si>
 </sst>
 </file>
@@ -991,6 +1016,110 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B732505C-285B-42B3-A042-6165BD789FC7}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>174</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40728223-3A6A-4F69-B5D3-677705D79A5B}">
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1127,7 +1256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F468D78-F21B-4C38-BEE1-9674FBD41E4C}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1253,7 +1382,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{293552FE-154F-41A7-B02B-483E9B842FD1}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAACABD3-4A89-4380-BD5F-E498C976DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1386320-7780-4965-A103-515928FCD02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Piadineria La Salsiccia" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,8 @@
     <sheet name="Leoni di Ricky" sheetId="14" r:id="rId10"/>
     <sheet name="Fatine FC" sheetId="11" r:id="rId11"/>
     <sheet name="Barrio Boys" sheetId="13" r:id="rId12"/>
-    <sheet name="Senza Nome" sheetId="12" r:id="rId13"/>
+    <sheet name="FC Internazionale Rovigo" sheetId="15" r:id="rId13"/>
+    <sheet name="Senza Nome" sheetId="12" r:id="rId14"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="194">
   <si>
     <t>Nome</t>
   </si>
@@ -565,6 +566,60 @@
   </si>
   <si>
     <t>Barzaghideanu</t>
+  </si>
+  <si>
+    <t>Bogdan</t>
+  </si>
+  <si>
+    <t>Atamanyuk</t>
+  </si>
+  <si>
+    <t>Ivan Denis</t>
+  </si>
+  <si>
+    <t>Sheverak</t>
+  </si>
+  <si>
+    <t>Mohamed</t>
+  </si>
+  <si>
+    <t>Iaich</t>
+  </si>
+  <si>
+    <t>Andolfo</t>
+  </si>
+  <si>
+    <t>Ahmed</t>
+  </si>
+  <si>
+    <t>Zouzaf</t>
+  </si>
+  <si>
+    <t>Youssef</t>
+  </si>
+  <si>
+    <t>Hamza</t>
+  </si>
+  <si>
+    <t>Agribi</t>
+  </si>
+  <si>
+    <t>Khalid</t>
+  </si>
+  <si>
+    <t>Bennoune</t>
+  </si>
+  <si>
+    <t>Yassine</t>
+  </si>
+  <si>
+    <t>Sohayb</t>
+  </si>
+  <si>
+    <t>Abdessamad</t>
+  </si>
+  <si>
+    <t>Baghrouch</t>
   </si>
 </sst>
 </file>
@@ -1383,6 +1438,113 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FF7E75F-A1E8-4699-A05F-FAA9BF9A7835}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>190</v>
+      </c>
+      <c r="B10" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{293552FE-154F-41A7-B02B-483E9B842FD1}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1386320-7780-4965-A103-515928FCD02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136418D2-628D-4C23-8F85-3352B8823D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Piadineria La Salsiccia" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,8 @@
     <sheet name="Fatine FC" sheetId="11" r:id="rId11"/>
     <sheet name="Barrio Boys" sheetId="13" r:id="rId12"/>
     <sheet name="FC Internazionale Rovigo" sheetId="15" r:id="rId13"/>
-    <sheet name="Senza Nome" sheetId="12" r:id="rId14"/>
+    <sheet name="Beverton" sheetId="16" r:id="rId14"/>
+    <sheet name="Senza Nome" sheetId="12" r:id="rId15"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="201">
   <si>
     <t>Nome</t>
   </si>
@@ -620,6 +621,27 @@
   </si>
   <si>
     <t>Baghrouch</t>
+  </si>
+  <si>
+    <t>Samuel</t>
+  </si>
+  <si>
+    <t>Mattiello</t>
+  </si>
+  <si>
+    <t>Bonsu</t>
+  </si>
+  <si>
+    <t>Vendramin</t>
+  </si>
+  <si>
+    <t>Christian</t>
+  </si>
+  <si>
+    <t>Zuccato</t>
+  </si>
+  <si>
+    <t>Bartolomei</t>
   </si>
 </sst>
 </file>
@@ -1545,6 +1567,99 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8756BF2-3DF4-4BAB-97A6-A3FB6209375F}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C7">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{293552FE-154F-41A7-B02B-483E9B842FD1}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136418D2-628D-4C23-8F85-3352B8823D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5009D914-81C2-48A9-A555-D2E6A47236EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" firstSheet="11" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Piadineria La Salsiccia" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,8 @@
     <sheet name="Barrio Boys" sheetId="13" r:id="rId12"/>
     <sheet name="FC Internazionale Rovigo" sheetId="15" r:id="rId13"/>
     <sheet name="Beverton" sheetId="16" r:id="rId14"/>
-    <sheet name="Senza Nome" sheetId="12" r:id="rId15"/>
+    <sheet name="Boldò Glimt" sheetId="17" r:id="rId15"/>
+    <sheet name="Senza Nome" sheetId="12" r:id="rId16"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="210">
   <si>
     <t>Nome</t>
   </si>
@@ -642,6 +643,33 @@
   </si>
   <si>
     <t>Bartolomei</t>
+  </si>
+  <si>
+    <t>Bellucco</t>
+  </si>
+  <si>
+    <t>Bertipaglia</t>
+  </si>
+  <si>
+    <t>Cuccato</t>
+  </si>
+  <si>
+    <t>Verza</t>
+  </si>
+  <si>
+    <t>Neodo</t>
+  </si>
+  <si>
+    <t>Fabio</t>
+  </si>
+  <si>
+    <t>Ferrari</t>
+  </si>
+  <si>
+    <t>Morin</t>
+  </si>
+  <si>
+    <t>Cecconello</t>
   </si>
 </sst>
 </file>
@@ -1660,6 +1688,132 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{229326FE-2BDF-4BA1-9F63-ABF051A3058D}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>209</v>
+      </c>
+      <c r="C10">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{293552FE-154F-41A7-B02B-483E9B842FD1}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5009D914-81C2-48A9-A555-D2E6A47236EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FEEAF4-0A83-45A6-9BCE-2D66BB4A3257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" firstSheet="11" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Piadineria La Salsiccia" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="211">
   <si>
     <t>Nome</t>
   </si>
@@ -670,6 +670,9 @@
   </si>
   <si>
     <t>Cecconello</t>
+  </si>
+  <si>
+    <t>Baldon</t>
   </si>
 </sst>
 </file>
@@ -996,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -1095,23 +1098,34 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>19</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>20</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>11</v>
       </c>
     </row>

--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FEEAF4-0A83-45A6-9BCE-2D66BB4A3257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB2D2E2-C9ED-4433-9635-F1EDE8D8A1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Piadineria La Salsiccia" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <sheet name="FC Internazionale Rovigo" sheetId="15" r:id="rId13"/>
     <sheet name="Beverton" sheetId="16" r:id="rId14"/>
     <sheet name="Boldò Glimt" sheetId="17" r:id="rId15"/>
-    <sheet name="Senza Nome" sheetId="12" r:id="rId16"/>
+    <sheet name="MoViola Utd" sheetId="12" r:id="rId16"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="212">
   <si>
     <t>Nome</t>
   </si>
@@ -673,6 +673,9 @@
   </si>
   <si>
     <t>Baldon</t>
+  </si>
+  <si>
+    <t>Ferro</t>
   </si>
 </sst>
 </file>
@@ -1377,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F468D78-F21B-4C38-BEE1-9674FBD41E4C}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -1487,12 +1490,23 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>91</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>167</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>20</v>
       </c>
     </row>
@@ -2889,7 +2903,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE4569C5-F714-4D8F-9D9F-AD29189E5BA2}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2930,81 +2944,92 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>127</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="C5">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="C6">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C7">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C8">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="C9">
-        <v>63</v>
-      </c>
-      <c r="D9" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10">
+        <v>63</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>29</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>132</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>95</v>
       </c>
     </row>

--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB2D2E2-C9ED-4433-9635-F1EDE8D8A1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783415A7-320C-47AD-AF32-254961BFC1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" firstSheet="12" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Piadineria La Salsiccia" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="214">
   <si>
     <t>Nome</t>
   </si>
@@ -676,6 +676,12 @@
   </si>
   <si>
     <t>Ferro</t>
+  </si>
+  <si>
+    <t>Angelo</t>
+  </si>
+  <si>
+    <t>Redi</t>
   </si>
 </sst>
 </file>
@@ -1717,7 +1723,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{229326FE-2BDF-4BA1-9F63-ABF051A3058D}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -1769,70 +1775,81 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>212</v>
       </c>
       <c r="B5" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C7">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>206</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>206</v>
       </c>
       <c r="B9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C9">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>208</v>
+      </c>
+      <c r="C10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>209</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>21</v>
       </c>
     </row>
@@ -1867,9 +1884,6 @@
       <c r="B2" t="s">
         <v>143</v>
       </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -1877,6 +1891,9 @@
       </c>
       <c r="B3" t="s">
         <v>145</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">

--- a/squadre.xlsx
+++ b/squadre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783415A7-320C-47AD-AF32-254961BFC1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF10C6A-783B-421F-BF06-244558F6BD06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" firstSheet="12" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" firstSheet="8" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Piadineria La Salsiccia" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="216">
   <si>
     <t>Nome</t>
   </si>
@@ -682,6 +682,12 @@
   </si>
   <si>
     <t>Redi</t>
+  </si>
+  <si>
+    <t>Vlad Gabriel</t>
+  </si>
+  <si>
+    <t>Duminica</t>
   </si>
 </sst>
 </file>
@@ -1145,7 +1151,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B732505C-285B-42B3-A042-6165BD789FC7}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -1240,6 +1246,17 @@
       </c>
       <c r="C8">
         <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C9">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
